--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136418818</v>
       </c>
       <c r="B9" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136420235</v>
       </c>
       <c r="B10" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136419106</v>
       </c>
       <c r="B11" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136418818</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136420235</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136419106</v>
       </c>
       <c r="B11" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136418818</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136420235</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136419106</v>
       </c>
       <c r="B11" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 36266-2026 artfynd.xlsx
+++ b/artfynd/A 36266-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419022</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136419671</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136420196</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136420321</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136420398</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136420724</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136420832</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136418818</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136420235</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136419106</v>
       </c>
       <c r="B11" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
